--- a/data/input/preparation/ai_results/quality_reports/puma_disagreements_Leadership_context_human.xlsx
+++ b/data/input/preparation/ai_results/quality_reports/puma_disagreements_Leadership_context_human.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
